--- a/Detailed Race and Ethnicity/detailedRaceLinkShort.xlsx
+++ b/Detailed Race and Ethnicity/detailedRaceLinkShort.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\FusionData\OtherProjects\Population Data Task Force\Detailed Race and Ethnicity\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\FusionData\Population Task Force\Detailed Race and Ethnicity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{434F8BBF-5BAB-4CA0-BA8B-DA5567F578C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C18F9A94-AC23-4CC5-82BB-38CFFE6998FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25500" yWindow="990" windowWidth="21600" windowHeight="14115" activeTab="1" xr2:uid="{B39827AF-3832-4AC4-B840-2D8672BFD646}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="36135" windowHeight="18435" activeTab="1" xr2:uid="{B39827AF-3832-4AC4-B840-2D8672BFD646}"/>
   </bookViews>
   <sheets>
     <sheet name="Detailed RaceEthnicity Mapping" sheetId="4" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="5" r:id="rId2"/>
+    <sheet name="detailedRaceLink" sheetId="6" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1136" uniqueCount="230">
   <si>
     <t xml:space="preserve">WHITE  </t>
   </si>
@@ -443,6 +444,285 @@
   </si>
   <si>
     <t xml:space="preserve"> -</t>
+  </si>
+  <si>
+    <t>pums_raceName_2019</t>
+  </si>
+  <si>
+    <t>pums_raceName_2022</t>
+  </si>
+  <si>
+    <t>pums_raceName_2023</t>
+  </si>
+  <si>
+    <t>detailedRace_2019</t>
+  </si>
+  <si>
+    <t>detailedRace_2022</t>
+  </si>
+  <si>
+    <t>detailedRace_2023</t>
+  </si>
+  <si>
+    <t>raceGroup</t>
+  </si>
+  <si>
+    <t>AI/AN</t>
+  </si>
+  <si>
+    <t>Blackfeet Tribe of the Blackfeet Indian Reservation of Montana alone</t>
+  </si>
+  <si>
+    <t>Cherokee alone</t>
+  </si>
+  <si>
+    <t>Cherokee Nation alone</t>
+  </si>
+  <si>
+    <t>Cheyenne alone</t>
+  </si>
+  <si>
+    <t>Cheyenne River Sioux Tribe of the Cheyenne River Reservation, South Dakota alone</t>
+  </si>
+  <si>
+    <t>Chickasaw alone</t>
+  </si>
+  <si>
+    <t>The Chickasaw Nation alone</t>
+  </si>
+  <si>
+    <t>Chippewa alone</t>
+  </si>
+  <si>
+    <t>Choctaw alone</t>
+  </si>
+  <si>
+    <t>Comanche alone</t>
+  </si>
+  <si>
+    <t>Creek alone</t>
+  </si>
+  <si>
+    <t>Crow alone</t>
+  </si>
+  <si>
+    <t>Crow Tribe of Montana alone</t>
+  </si>
+  <si>
+    <t>Hopi alone</t>
+  </si>
+  <si>
+    <t>Hopi Tribe of Arizona alone</t>
+  </si>
+  <si>
+    <t>Iroquois alone</t>
+  </si>
+  <si>
+    <t>Lumbee alone</t>
+  </si>
+  <si>
+    <t>Lumbee Tribe of North Carolina alone</t>
+  </si>
+  <si>
+    <t>Mexican American Indian alone</t>
+  </si>
+  <si>
+    <t>The Muscogee (Creek) Nation alone</t>
+  </si>
+  <si>
+    <t>Navajo alone</t>
+  </si>
+  <si>
+    <t>Navajo Nation alone</t>
+  </si>
+  <si>
+    <t>Oglala Sioux Tribe alone</t>
+  </si>
+  <si>
+    <t>Pascua Yaqui Tribe of Arizona alone</t>
+  </si>
+  <si>
+    <t>Pima alone</t>
+  </si>
+  <si>
+    <t>Potawatomi alone</t>
+  </si>
+  <si>
+    <t>Pueblo alone</t>
+  </si>
+  <si>
+    <t>Puget Sound Salish alone</t>
+  </si>
+  <si>
+    <t>Rosebud Sioux Tribe of the Rosebud Indian Reservation, South Dakota alone</t>
+  </si>
+  <si>
+    <t>Seminole alone</t>
+  </si>
+  <si>
+    <t>Sioux alone</t>
+  </si>
+  <si>
+    <t>South American Indian alone</t>
+  </si>
+  <si>
+    <t>Tohono O'Odham alone</t>
+  </si>
+  <si>
+    <t>Tohono O'odham Nation of Arizona alone</t>
+  </si>
+  <si>
+    <t>Yaqui alone</t>
+  </si>
+  <si>
+    <t>Other specified American Indian tribes alone</t>
+  </si>
+  <si>
+    <t>All other specified American Indian tribe combinations</t>
+  </si>
+  <si>
+    <t>American Indian alone, not specified</t>
+  </si>
+  <si>
+    <t>All other American Indian tribes alone</t>
+  </si>
+  <si>
+    <t>Aztec alone</t>
+  </si>
+  <si>
+    <t>Inca alone</t>
+  </si>
+  <si>
+    <t>Maya alone</t>
+  </si>
+  <si>
+    <t>Mixtec alone</t>
+  </si>
+  <si>
+    <t>Taino alone</t>
+  </si>
+  <si>
+    <t>Tarasco (Purepecha) alone</t>
+  </si>
+  <si>
+    <t>All other Latin American Indian alone</t>
+  </si>
+  <si>
+    <t>Alaska Native tribes and villages alone</t>
+  </si>
+  <si>
+    <t>Other Alaska Native</t>
+  </si>
+  <si>
+    <t>Alaska Native alone, not specified</t>
+  </si>
+  <si>
+    <t>Other American Indian and Alaska Native specified</t>
+  </si>
+  <si>
+    <t>Other specified American Indian and Alaska Native combinations</t>
+  </si>
+  <si>
+    <t>AIAN_Other_Multiple</t>
+  </si>
+  <si>
+    <t>Other AI/AN</t>
+  </si>
+  <si>
+    <t>Other/Multi AIAN</t>
+  </si>
+  <si>
+    <t>American Indian and Alaska Native, not specified</t>
+  </si>
+  <si>
+    <t>American Indian and Alaska Native alone, not specified</t>
+  </si>
+  <si>
+    <t>Asian Indian</t>
+  </si>
+  <si>
+    <t>Bangladeshi</t>
+  </si>
+  <si>
+    <t>Other Asian</t>
+  </si>
+  <si>
+    <t>Chinese, except Taiwanese alone</t>
+  </si>
+  <si>
+    <t>Chinese</t>
+  </si>
+  <si>
+    <t>Taiwanese</t>
+  </si>
+  <si>
+    <t>Indonesian</t>
+  </si>
+  <si>
+    <t>Kazakh alone</t>
+  </si>
+  <si>
+    <t>Malaysian</t>
+  </si>
+  <si>
+    <t>Mien alone</t>
+  </si>
+  <si>
+    <t>Pakistani</t>
+  </si>
+  <si>
+    <t>Sikh alone</t>
+  </si>
+  <si>
+    <t>Sri Lankan</t>
+  </si>
+  <si>
+    <t>Uzbek alone</t>
+  </si>
+  <si>
+    <t>Multi-Asian</t>
+  </si>
+  <si>
+    <t>Other Asian alone and all Asian combinations</t>
+  </si>
+  <si>
+    <t>Other/Multi Asian</t>
+  </si>
+  <si>
+    <t>All other Spanish/Hispanic/Latino</t>
+  </si>
+  <si>
+    <t>Multi-Race</t>
+  </si>
+  <si>
+    <t>NH/PI</t>
+  </si>
+  <si>
+    <t>Tongan</t>
+  </si>
+  <si>
+    <t>Chamorro alone</t>
+  </si>
+  <si>
+    <t>Chuukese alone</t>
+  </si>
+  <si>
+    <t>Other/Multi NHPI</t>
+  </si>
+  <si>
+    <t>Guamanian alone</t>
+  </si>
+  <si>
+    <t>Other Pac. Isl.</t>
+  </si>
+  <si>
+    <t>Fijian</t>
+  </si>
+  <si>
+    <t>Other Native Hawaiian and Other Pacific Islander (NHPI) alone and all NHPI combinations</t>
+  </si>
+  <si>
+    <t>Total</t>
   </si>
 </sst>
 </file>
@@ -466,7 +746,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -494,6 +774,48 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF9999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -653,44 +975,43 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -716,21 +1037,29 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -755,9 +1084,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -795,7 +1124,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -901,7 +1230,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1043,7 +1372,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1054,840 +1383,839 @@
   <dimension ref="B1:E69"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="38.85546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="60.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="2.28515625" customWidth="1"/>
+    <col min="2" max="2" width="38.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="60.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:5" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="38" t="s">
         <v>127</v>
       </c>
-      <c r="C2" s="37" t="s">
+      <c r="C2" s="36" t="s">
         <v>134</v>
       </c>
-      <c r="D2" s="37"/>
-      <c r="E2" s="38"/>
-    </row>
-    <row r="3" spans="2:5" s="2" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="40"/>
-      <c r="C3" s="9" t="s">
+      <c r="D2" s="36"/>
+      <c r="E2" s="37"/>
+    </row>
+    <row r="3" spans="2:5" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="39"/>
+      <c r="C3" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="10" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="4" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="36" t="s">
+      <c r="B4" s="35" t="s">
         <v>128</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="D4" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="E4" s="14" t="s">
+      <c r="D4" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="E4" s="13" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="5" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="36"/>
-      <c r="C5" s="15" t="s">
+      <c r="B5" s="35"/>
+      <c r="C5" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E5" s="17" t="s">
+      <c r="D5" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E5" s="16" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="6" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="36"/>
-      <c r="C6" s="15" t="s">
+      <c r="B6" s="35"/>
+      <c r="C6" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="D6" s="16"/>
-      <c r="E6" s="17" t="s">
+      <c r="D6" s="15"/>
+      <c r="E6" s="16" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="7" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="36"/>
-      <c r="C7" s="15" t="s">
+      <c r="B7" s="35"/>
+      <c r="C7" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="16" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="8" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="36"/>
-      <c r="C8" s="15" t="s">
+      <c r="B8" s="35"/>
+      <c r="C8" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E8" s="17" t="s">
+      <c r="D8" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E8" s="16" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="9" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="36"/>
-      <c r="C9" s="15" t="s">
+      <c r="B9" s="35"/>
+      <c r="C9" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="D9" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E9" s="17" t="s">
+      <c r="D9" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E9" s="16" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="10" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="36"/>
-      <c r="C10" s="15" t="s">
+      <c r="B10" s="35"/>
+      <c r="C10" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="D10" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E10" s="17" t="s">
+      <c r="D10" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E10" s="16" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="11" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="36"/>
-      <c r="C11" s="15" t="s">
+      <c r="B11" s="35"/>
+      <c r="C11" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="E11" s="17" t="s">
+      <c r="E11" s="16" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="12" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="36"/>
-      <c r="C12" s="18" t="s">
+      <c r="B12" s="35"/>
+      <c r="C12" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="E12" s="20" t="s">
+      <c r="E12" s="19" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="13" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="36" t="s">
+      <c r="B13" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="13" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="14" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="36"/>
-      <c r="C14" s="15" t="s">
+      <c r="B14" s="35"/>
+      <c r="C14" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="17" t="s">
+      <c r="E14" s="16" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="15" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="36"/>
-      <c r="C15" s="15" t="s">
+      <c r="B15" s="35"/>
+      <c r="C15" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="D15" s="16" t="s">
+      <c r="D15" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="17" t="s">
+      <c r="E15" s="16" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="16" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="36"/>
-      <c r="C16" s="15" t="s">
+      <c r="B16" s="35"/>
+      <c r="C16" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="E16" s="17" t="s">
+      <c r="E16" s="16" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="17" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="36"/>
-      <c r="C17" s="15" t="s">
+      <c r="B17" s="35"/>
+      <c r="C17" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="D17" s="16" t="s">
+      <c r="D17" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E17" s="17" t="s">
+      <c r="E17" s="16" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="18" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="36"/>
-      <c r="C18" s="15" t="s">
+      <c r="B18" s="35"/>
+      <c r="C18" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="D18" s="16" t="s">
+      <c r="D18" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="E18" s="17" t="s">
+      <c r="E18" s="16" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="19" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="36"/>
-      <c r="C19" s="15" t="s">
+      <c r="B19" s="35"/>
+      <c r="C19" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="D19" s="16" t="s">
+      <c r="D19" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="E19" s="17" t="s">
+      <c r="E19" s="16" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="20" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="36"/>
-      <c r="C20" s="15" t="s">
+      <c r="B20" s="35"/>
+      <c r="C20" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="D20" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="E20" s="17" t="s">
+      <c r="E20" s="16" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="21" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="36"/>
-      <c r="C21" s="15" t="s">
+      <c r="B21" s="35"/>
+      <c r="C21" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="D21" s="16" t="s">
+      <c r="D21" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="E21" s="17" t="s">
+      <c r="E21" s="16" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="22" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="36"/>
-      <c r="C22" s="15" t="s">
+      <c r="B22" s="35"/>
+      <c r="C22" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="D22" s="16" t="s">
+      <c r="D22" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="E22" s="17" t="s">
+      <c r="E22" s="16" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="23" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="36"/>
-      <c r="C23" s="15" t="s">
+      <c r="B23" s="35"/>
+      <c r="C23" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="D23" s="16" t="s">
+      <c r="D23" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="E23" s="17" t="s">
+      <c r="E23" s="16" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="24" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="36"/>
-      <c r="C24" s="15" t="s">
+      <c r="B24" s="35"/>
+      <c r="C24" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="D24" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E24" s="17" t="s">
+      <c r="D24" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E24" s="16" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="25" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="36"/>
-      <c r="C25" s="15" t="s">
+      <c r="B25" s="35"/>
+      <c r="C25" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="D25" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E25" s="17" t="s">
+      <c r="D25" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E25" s="16" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="26" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="36"/>
-      <c r="C26" s="15" t="s">
+      <c r="B26" s="35"/>
+      <c r="C26" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D26" s="16" t="s">
+      <c r="D26" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="E26" s="17" t="s">
+      <c r="E26" s="16" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="27" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="36"/>
-      <c r="C27" s="15" t="s">
+      <c r="B27" s="35"/>
+      <c r="C27" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="D27" s="16" t="s">
+      <c r="D27" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="E27" s="17" t="s">
+      <c r="E27" s="16" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="28" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="36"/>
-      <c r="C28" s="15" t="s">
+      <c r="B28" s="35"/>
+      <c r="C28" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="D28" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E28" s="17" t="s">
+      <c r="D28" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E28" s="16" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="29" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="36"/>
-      <c r="C29" s="15" t="s">
+      <c r="B29" s="35"/>
+      <c r="C29" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="D29" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E29" s="17" t="s">
+      <c r="D29" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E29" s="16" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="30" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="36"/>
-      <c r="C30" s="15" t="s">
+      <c r="B30" s="35"/>
+      <c r="C30" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="D30" s="16" t="s">
+      <c r="D30" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="E30" s="17" t="s">
+      <c r="E30" s="16" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="31" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="36"/>
-      <c r="C31" s="15" t="s">
+      <c r="B31" s="35"/>
+      <c r="C31" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="D31" s="16" t="s">
+      <c r="D31" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="E31" s="17" t="s">
+      <c r="E31" s="16" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="32" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="36"/>
-      <c r="C32" s="15" t="s">
+      <c r="B32" s="35"/>
+      <c r="C32" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="D32" s="16" t="s">
+      <c r="D32" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="E32" s="17" t="s">
+      <c r="E32" s="16" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="33" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="36"/>
-      <c r="C33" s="15" t="s">
+      <c r="B33" s="35"/>
+      <c r="C33" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="D33" s="16" t="s">
+      <c r="D33" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="E33" s="17" t="s">
+      <c r="E33" s="16" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="34" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="36"/>
-      <c r="C34" s="18" t="s">
+      <c r="B34" s="35"/>
+      <c r="C34" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D34" s="19" t="s">
+      <c r="D34" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="E34" s="20" t="s">
+      <c r="E34" s="19" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="35" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="36" t="s">
+      <c r="B35" s="35" t="s">
         <v>129</v>
       </c>
-      <c r="C35" s="12" t="s">
+      <c r="C35" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="D35" s="13" t="s">
+      <c r="D35" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="E35" s="14" t="s">
+      <c r="E35" s="13" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="36" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="36"/>
-      <c r="C36" s="15" t="s">
+      <c r="B36" s="35"/>
+      <c r="C36" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="D36" s="16" t="s">
+      <c r="D36" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="E36" s="17" t="s">
+      <c r="E36" s="16" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="37" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="36"/>
-      <c r="C37" s="15" t="s">
+      <c r="B37" s="35"/>
+      <c r="C37" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="D37" s="16" t="s">
+      <c r="D37" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="E37" s="17" t="s">
+      <c r="E37" s="16" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="38" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="36"/>
-      <c r="C38" s="15" t="s">
+      <c r="B38" s="35"/>
+      <c r="C38" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="D38" s="16" t="s">
+      <c r="D38" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="E38" s="17" t="s">
+      <c r="E38" s="16" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="39" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="36"/>
-      <c r="C39" s="15" t="s">
+      <c r="B39" s="35"/>
+      <c r="C39" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="D39" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E39" s="17" t="s">
+      <c r="D39" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E39" s="16" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="40" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="36"/>
-      <c r="C40" s="15" t="s">
+      <c r="B40" s="35"/>
+      <c r="C40" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="D40" s="16" t="s">
+      <c r="D40" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="E40" s="17" t="s">
+      <c r="E40" s="16" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="41" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="36"/>
-      <c r="C41" s="15" t="s">
+      <c r="B41" s="35"/>
+      <c r="C41" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="D41" s="16" t="s">
+      <c r="D41" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="E41" s="17" t="s">
+      <c r="E41" s="16" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="42" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="36"/>
-      <c r="C42" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="D42" s="19" t="s">
+      <c r="B42" s="35"/>
+      <c r="C42" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="D42" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="E42" s="20" t="s">
+      <c r="E42" s="19" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="43" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="8" t="s">
+      <c r="B43" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="C43" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D43" s="3" t="s">
+      <c r="D43" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E43" s="5" t="s">
+      <c r="E43" s="4" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="44" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="8" t="s">
+      <c r="B44" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="C44" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
+      <c r="D44" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E44" s="5" t="s">
+      <c r="E44" s="4" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="45" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B45" s="8" t="s">
+      <c r="B45" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="C45" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="D45" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E45" s="5" t="s">
+      <c r="E45" s="4" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="46" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="8" t="s">
+      <c r="B46" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="C46" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D46" s="3" t="s">
+      <c r="D46" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E46" s="5" t="s">
+      <c r="E46" s="4" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="47" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B47" s="36" t="s">
+      <c r="B47" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="C47" s="12" t="s">
+      <c r="C47" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="D47" s="13" t="s">
+      <c r="D47" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="E47" s="14" t="s">
+      <c r="E47" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="48" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="36"/>
-      <c r="C48" s="15" t="s">
+      <c r="B48" s="35"/>
+      <c r="C48" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="D48" s="16" t="s">
+      <c r="D48" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="E48" s="17" t="s">
+      <c r="E48" s="16" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="49" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="36"/>
-      <c r="C49" s="15" t="s">
+      <c r="B49" s="35"/>
+      <c r="C49" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="D49" s="16" t="s">
+      <c r="D49" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="E49" s="17" t="s">
+      <c r="E49" s="16" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="50" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="36"/>
-      <c r="C50" s="15" t="s">
+      <c r="B50" s="35"/>
+      <c r="C50" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="D50" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E50" s="17" t="s">
+      <c r="D50" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E50" s="16" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="51" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B51" s="36"/>
-      <c r="C51" s="15" t="s">
+      <c r="B51" s="35"/>
+      <c r="C51" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="D51" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E51" s="17" t="s">
+      <c r="D51" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E51" s="16" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="52" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="36"/>
-      <c r="C52" s="15" t="s">
+      <c r="B52" s="35"/>
+      <c r="C52" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="D52" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E52" s="17" t="s">
+      <c r="D52" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E52" s="16" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="53" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B53" s="36"/>
-      <c r="C53" s="15" t="s">
+      <c r="B53" s="35"/>
+      <c r="C53" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="D53" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E53" s="17" t="s">
+      <c r="D53" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E53" s="16" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="54" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="36"/>
-      <c r="C54" s="15" t="s">
+      <c r="B54" s="35"/>
+      <c r="C54" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="D54" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E54" s="17" t="s">
+      <c r="D54" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E54" s="16" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="55" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="36"/>
-      <c r="C55" s="15" t="s">
+      <c r="B55" s="35"/>
+      <c r="C55" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="D55" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E55" s="17" t="s">
+      <c r="D55" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E55" s="16" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="56" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="36"/>
-      <c r="C56" s="15" t="s">
+      <c r="B56" s="35"/>
+      <c r="C56" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="D56" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E56" s="17" t="s">
+      <c r="D56" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E56" s="16" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="57" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="36"/>
-      <c r="C57" s="15" t="s">
+      <c r="B57" s="35"/>
+      <c r="C57" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="D57" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E57" s="17" t="s">
+      <c r="D57" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E57" s="16" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="58" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="36"/>
-      <c r="C58" s="15" t="s">
+      <c r="B58" s="35"/>
+      <c r="C58" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="D58" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E58" s="17" t="s">
+      <c r="D58" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E58" s="16" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="59" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="36"/>
-      <c r="C59" s="15" t="s">
+      <c r="B59" s="35"/>
+      <c r="C59" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="D59" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E59" s="17" t="s">
+      <c r="D59" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E59" s="16" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="60" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="36"/>
-      <c r="C60" s="15" t="s">
+      <c r="B60" s="35"/>
+      <c r="C60" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="D60" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E60" s="17" t="s">
+      <c r="D60" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E60" s="16" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="61" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="36"/>
-      <c r="C61" s="15" t="s">
+      <c r="B61" s="35"/>
+      <c r="C61" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="D61" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E61" s="17" t="s">
+      <c r="D61" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E61" s="16" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="62" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="36"/>
-      <c r="C62" s="15" t="s">
+      <c r="B62" s="35"/>
+      <c r="C62" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="D62" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E62" s="17" t="s">
+      <c r="D62" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E62" s="16" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="63" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B63" s="36"/>
-      <c r="C63" s="15" t="s">
+      <c r="B63" s="35"/>
+      <c r="C63" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="D63" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E63" s="17" t="s">
+      <c r="D63" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E63" s="16" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="64" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="36"/>
-      <c r="C64" s="15" t="s">
+      <c r="B64" s="35"/>
+      <c r="C64" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="D64" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E64" s="17" t="s">
+      <c r="D64" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E64" s="16" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="65" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="36"/>
-      <c r="C65" s="15" t="s">
+      <c r="B65" s="35"/>
+      <c r="C65" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="D65" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E65" s="17" t="s">
+      <c r="D65" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E65" s="16" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="66" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B66" s="36"/>
-      <c r="C66" s="15" t="s">
+      <c r="B66" s="35"/>
+      <c r="C66" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="D66" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E66" s="17" t="s">
+      <c r="D66" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E66" s="16" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="67" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B67" s="36"/>
-      <c r="C67" s="15" t="s">
+      <c r="B67" s="35"/>
+      <c r="C67" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="D67" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E67" s="17" t="s">
+      <c r="D67" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E67" s="16" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="68" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="36"/>
-      <c r="C68" s="15" t="s">
+      <c r="B68" s="35"/>
+      <c r="C68" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="D68" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E68" s="17" t="s">
+      <c r="D68" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E68" s="16" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="69" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B69" s="36"/>
-      <c r="C69" s="18" t="s">
+      <c r="B69" s="35"/>
+      <c r="C69" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="D69" s="19" t="s">
+      <c r="D69" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="E69" s="20" t="s">
+      <c r="E69" s="19" t="s">
         <v>108</v>
       </c>
     </row>
@@ -1902,848 +2230,3338 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;13&amp;K000000 Confidential - Low</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3A20FD9-A765-43FF-B42F-05D6803E045A}">
+  <dimension ref="A1:G115"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="50.7109375" customWidth="1"/>
+    <col min="3" max="3" width="82.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.85546875" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="F2" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="G2" s="40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="40" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="40" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="40" t="s">
+        <v>145</v>
+      </c>
+      <c r="D3" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" s="40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="40" t="s">
+        <v>146</v>
+      </c>
+      <c r="B4" s="40" t="s">
+        <v>146</v>
+      </c>
+      <c r="C4" s="40" t="s">
+        <v>147</v>
+      </c>
+      <c r="D4" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" s="40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="41" t="s">
+        <v>148</v>
+      </c>
+      <c r="B5" s="41"/>
+      <c r="C5" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="D5" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="40" t="s">
+        <v>150</v>
+      </c>
+      <c r="B6" s="40" t="s">
+        <v>150</v>
+      </c>
+      <c r="C6" s="40" t="s">
+        <v>151</v>
+      </c>
+      <c r="D6" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="40" t="s">
+        <v>152</v>
+      </c>
+      <c r="B7" s="40" t="s">
+        <v>152</v>
+      </c>
+      <c r="C7" s="40"/>
+      <c r="D7" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="40" t="s">
+        <v>153</v>
+      </c>
+      <c r="B8" s="40" t="s">
+        <v>153</v>
+      </c>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="41" t="s">
+        <v>154</v>
+      </c>
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="40" t="s">
+        <v>155</v>
+      </c>
+      <c r="B10" s="40" t="s">
+        <v>155</v>
+      </c>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" s="40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="40" t="s">
+        <v>156</v>
+      </c>
+      <c r="B11" s="40" t="s">
+        <v>156</v>
+      </c>
+      <c r="C11" s="40" t="s">
+        <v>157</v>
+      </c>
+      <c r="D11" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="G11" s="40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="40" t="s">
+        <v>158</v>
+      </c>
+      <c r="B12" s="40" t="s">
+        <v>158</v>
+      </c>
+      <c r="C12" s="40" t="s">
+        <v>159</v>
+      </c>
+      <c r="D12" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12" s="40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="40" t="s">
+        <v>160</v>
+      </c>
+      <c r="B13" s="40" t="s">
+        <v>160</v>
+      </c>
+      <c r="C13" s="40"/>
+      <c r="D13" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="F13" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" s="40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="40" t="s">
+        <v>161</v>
+      </c>
+      <c r="B14" s="40" t="s">
+        <v>161</v>
+      </c>
+      <c r="C14" s="40" t="s">
+        <v>162</v>
+      </c>
+      <c r="D14" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="F14" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="G14" s="40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="40" t="s">
+        <v>163</v>
+      </c>
+      <c r="B15" s="40" t="s">
+        <v>163</v>
+      </c>
+      <c r="C15" s="40"/>
+      <c r="D15" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="F15" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="G15" s="40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="40"/>
+      <c r="B16" s="40"/>
+      <c r="C16" s="40" t="s">
+        <v>164</v>
+      </c>
+      <c r="D16" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="F16" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="G16" s="40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="40" t="s">
+        <v>165</v>
+      </c>
+      <c r="B17" s="40" t="s">
+        <v>165</v>
+      </c>
+      <c r="C17" s="40" t="s">
+        <v>166</v>
+      </c>
+      <c r="D17" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E17" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="F17" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="G17" s="40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="40"/>
+      <c r="B18" s="40"/>
+      <c r="C18" s="40" t="s">
+        <v>167</v>
+      </c>
+      <c r="D18" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="F18" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="G18" s="40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="40"/>
+      <c r="B19" s="40"/>
+      <c r="C19" s="40" t="s">
+        <v>168</v>
+      </c>
+      <c r="D19" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E19" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="F19" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="G19" s="40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="40" t="s">
+        <v>169</v>
+      </c>
+      <c r="B20" s="40" t="s">
+        <v>169</v>
+      </c>
+      <c r="C20" s="40"/>
+      <c r="D20" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E20" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="F20" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="G20" s="40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="40" t="s">
+        <v>170</v>
+      </c>
+      <c r="B21" s="40" t="s">
+        <v>170</v>
+      </c>
+      <c r="C21" s="40"/>
+      <c r="D21" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E21" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="F21" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="G21" s="40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="40" t="s">
+        <v>171</v>
+      </c>
+      <c r="B22" s="40" t="s">
+        <v>171</v>
+      </c>
+      <c r="C22" s="40"/>
+      <c r="D22" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E22" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="F22" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="G22" s="40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="40" t="s">
+        <v>172</v>
+      </c>
+      <c r="B23" s="40" t="s">
+        <v>172</v>
+      </c>
+      <c r="C23" s="40"/>
+      <c r="D23" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="F23" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="G23" s="40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="40"/>
+      <c r="B24" s="40"/>
+      <c r="C24" s="40" t="s">
+        <v>173</v>
+      </c>
+      <c r="D24" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E24" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="F24" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="G24" s="40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="41" t="s">
+        <v>174</v>
+      </c>
+      <c r="B25" s="41"/>
+      <c r="C25" s="41"/>
+      <c r="D25" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E25" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="F25" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="G25" s="40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="40" t="s">
+        <v>175</v>
+      </c>
+      <c r="B26" s="40" t="s">
+        <v>175</v>
+      </c>
+      <c r="C26" s="40"/>
+      <c r="D26" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E26" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="F26" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="G26" s="40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="40" t="s">
+        <v>176</v>
+      </c>
+      <c r="B27" s="40" t="s">
+        <v>176</v>
+      </c>
+      <c r="C27" s="40"/>
+      <c r="D27" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E27" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="F27" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="G27" s="40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="40" t="s">
+        <v>177</v>
+      </c>
+      <c r="B28" s="40" t="s">
+        <v>177</v>
+      </c>
+      <c r="C28" s="40" t="s">
+        <v>178</v>
+      </c>
+      <c r="D28" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E28" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="F28" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="G28" s="40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="40" t="s">
+        <v>179</v>
+      </c>
+      <c r="B29" s="40" t="s">
+        <v>179</v>
+      </c>
+      <c r="C29" s="40"/>
+      <c r="D29" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E29" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="F29" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="G29" s="40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="40" t="s">
+        <v>180</v>
+      </c>
+      <c r="B30" s="40" t="s">
+        <v>180</v>
+      </c>
+      <c r="C30" s="40"/>
+      <c r="D30" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E30" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="F30" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="G30" s="40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="40" t="s">
+        <v>181</v>
+      </c>
+      <c r="B31" s="40" t="s">
+        <v>181</v>
+      </c>
+      <c r="C31" s="40"/>
+      <c r="D31" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E31" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="F31" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="G31" s="40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="40" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="40" t="s">
+        <v>41</v>
+      </c>
+      <c r="C32" s="40" t="s">
+        <v>182</v>
+      </c>
+      <c r="D32" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E32" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="F32" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="G32" s="40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="40"/>
+      <c r="B33" s="40"/>
+      <c r="C33" s="40" t="s">
+        <v>183</v>
+      </c>
+      <c r="D33" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E33" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="F33" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="G33" s="40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="40"/>
+      <c r="B34" s="40"/>
+      <c r="C34" s="40" t="s">
+        <v>184</v>
+      </c>
+      <c r="D34" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E34" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="F34" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="G34" s="40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="40"/>
+      <c r="B35" s="40"/>
+      <c r="C35" s="40" t="s">
+        <v>185</v>
+      </c>
+      <c r="D35" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E35" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="F35" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="G35" s="40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="40"/>
+      <c r="B36" s="40"/>
+      <c r="C36" s="40" t="s">
+        <v>186</v>
+      </c>
+      <c r="D36" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E36" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="F36" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="G36" s="40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="40"/>
+      <c r="B37" s="40"/>
+      <c r="C37" s="40" t="s">
+        <v>187</v>
+      </c>
+      <c r="D37" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E37" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="F37" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="G37" s="40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="40"/>
+      <c r="B38" s="40"/>
+      <c r="C38" s="40" t="s">
+        <v>188</v>
+      </c>
+      <c r="D38" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E38" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="F38" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="G38" s="40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="40"/>
+      <c r="B39" s="40"/>
+      <c r="C39" s="40" t="s">
+        <v>189</v>
+      </c>
+      <c r="D39" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E39" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="F39" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="G39" s="40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="40"/>
+      <c r="B40" s="40"/>
+      <c r="C40" s="40" t="s">
+        <v>190</v>
+      </c>
+      <c r="D40" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E40" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="F40" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="G40" s="40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="B41" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="C41" s="40"/>
+      <c r="D41" s="40" t="s">
+        <v>81</v>
+      </c>
+      <c r="E41" s="40" t="s">
+        <v>81</v>
+      </c>
+      <c r="F41" s="40" t="s">
+        <v>81</v>
+      </c>
+      <c r="G41" s="40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="B42" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="C42" s="40"/>
+      <c r="D42" s="40" t="s">
+        <v>81</v>
+      </c>
+      <c r="E42" s="40" t="s">
+        <v>81</v>
+      </c>
+      <c r="F42" s="40" t="s">
+        <v>81</v>
+      </c>
+      <c r="G42" s="40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="40" t="s">
+        <v>44</v>
+      </c>
+      <c r="B43" s="40" t="s">
+        <v>44</v>
+      </c>
+      <c r="C43" s="40"/>
+      <c r="D43" s="40" t="s">
+        <v>81</v>
+      </c>
+      <c r="E43" s="40" t="s">
+        <v>81</v>
+      </c>
+      <c r="F43" s="40" t="s">
+        <v>81</v>
+      </c>
+      <c r="G43" s="40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="40" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44" s="40" t="s">
+        <v>45</v>
+      </c>
+      <c r="C44" s="40"/>
+      <c r="D44" s="40" t="s">
+        <v>81</v>
+      </c>
+      <c r="E44" s="40" t="s">
+        <v>81</v>
+      </c>
+      <c r="F44" s="40" t="s">
+        <v>81</v>
+      </c>
+      <c r="G44" s="40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="B45" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="C45" s="40"/>
+      <c r="D45" s="40" t="s">
+        <v>81</v>
+      </c>
+      <c r="E45" s="40" t="s">
+        <v>81</v>
+      </c>
+      <c r="F45" s="40" t="s">
+        <v>81</v>
+      </c>
+      <c r="G45" s="40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="40"/>
+      <c r="B46" s="40"/>
+      <c r="C46" s="40" t="s">
+        <v>191</v>
+      </c>
+      <c r="D46" s="40" t="s">
+        <v>81</v>
+      </c>
+      <c r="E46" s="40" t="s">
+        <v>81</v>
+      </c>
+      <c r="F46" s="40" t="s">
+        <v>81</v>
+      </c>
+      <c r="G46" s="40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="40" t="s">
+        <v>192</v>
+      </c>
+      <c r="B47" s="40" t="s">
+        <v>192</v>
+      </c>
+      <c r="C47" s="40" t="s">
+        <v>193</v>
+      </c>
+      <c r="D47" s="40" t="s">
+        <v>81</v>
+      </c>
+      <c r="E47" s="40" t="s">
+        <v>81</v>
+      </c>
+      <c r="F47" s="40" t="s">
+        <v>81</v>
+      </c>
+      <c r="G47" s="40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="40" t="s">
+        <v>194</v>
+      </c>
+      <c r="B48" s="40" t="s">
+        <v>194</v>
+      </c>
+      <c r="C48" s="40" t="s">
+        <v>195</v>
+      </c>
+      <c r="D48" s="40" t="s">
+        <v>196</v>
+      </c>
+      <c r="E48" s="40" t="s">
+        <v>197</v>
+      </c>
+      <c r="F48" s="40" t="s">
+        <v>198</v>
+      </c>
+      <c r="G48" s="40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="40" t="s">
+        <v>199</v>
+      </c>
+      <c r="B49" s="40" t="s">
+        <v>199</v>
+      </c>
+      <c r="C49" s="40" t="s">
+        <v>200</v>
+      </c>
+      <c r="D49" s="40" t="s">
+        <v>196</v>
+      </c>
+      <c r="E49" s="40" t="s">
+        <v>197</v>
+      </c>
+      <c r="F49" s="40" t="s">
+        <v>198</v>
+      </c>
+      <c r="G49" s="40" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="42" t="s">
+        <v>47</v>
+      </c>
+      <c r="B50" s="42" t="s">
+        <v>47</v>
+      </c>
+      <c r="C50" s="42" t="s">
+        <v>47</v>
+      </c>
+      <c r="D50" s="41" t="s">
+        <v>117</v>
+      </c>
+      <c r="E50" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="F50" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="G50" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="42" t="s">
+        <v>48</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>48</v>
+      </c>
+      <c r="C51" s="42" t="s">
+        <v>48</v>
+      </c>
+      <c r="D51" s="41" t="s">
+        <v>117</v>
+      </c>
+      <c r="E51" s="41" t="s">
+        <v>202</v>
+      </c>
+      <c r="F51" s="41" t="s">
+        <v>202</v>
+      </c>
+      <c r="G51" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="B52" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="C52" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="D52" s="42" t="s">
+        <v>26</v>
+      </c>
+      <c r="E52" s="42" t="s">
+        <v>203</v>
+      </c>
+      <c r="F52" s="42" t="s">
+        <v>203</v>
+      </c>
+      <c r="G52" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" s="42" t="s">
+        <v>50</v>
+      </c>
+      <c r="B53" s="42" t="s">
+        <v>50</v>
+      </c>
+      <c r="C53" s="42" t="s">
+        <v>50</v>
+      </c>
+      <c r="D53" s="42" t="s">
+        <v>26</v>
+      </c>
+      <c r="E53" s="42" t="s">
+        <v>203</v>
+      </c>
+      <c r="F53" s="42" t="s">
+        <v>203</v>
+      </c>
+      <c r="G53" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="42" t="s">
+        <v>51</v>
+      </c>
+      <c r="B54" s="42" t="s">
+        <v>51</v>
+      </c>
+      <c r="C54" s="42" t="s">
+        <v>51</v>
+      </c>
+      <c r="D54" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="E54" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="F54" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="G54" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="42" t="s">
+        <v>52</v>
+      </c>
+      <c r="B55" s="42" t="s">
+        <v>52</v>
+      </c>
+      <c r="C55" s="42" t="s">
+        <v>204</v>
+      </c>
+      <c r="D55" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="E55" s="41" t="s">
+        <v>205</v>
+      </c>
+      <c r="F55" s="41" t="s">
+        <v>205</v>
+      </c>
+      <c r="G55" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="B56" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="C56" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="D56" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="E56" s="41" t="s">
+        <v>206</v>
+      </c>
+      <c r="F56" s="41" t="s">
+        <v>206</v>
+      </c>
+      <c r="G56" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="42" t="s">
+        <v>54</v>
+      </c>
+      <c r="B57" s="42" t="s">
+        <v>54</v>
+      </c>
+      <c r="C57" s="42" t="s">
+        <v>54</v>
+      </c>
+      <c r="D57" s="42" t="s">
+        <v>22</v>
+      </c>
+      <c r="E57" s="42" t="s">
+        <v>22</v>
+      </c>
+      <c r="F57" s="42" t="s">
+        <v>22</v>
+      </c>
+      <c r="G57" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="42" t="s">
+        <v>55</v>
+      </c>
+      <c r="B58" s="42" t="s">
+        <v>55</v>
+      </c>
+      <c r="C58" s="42" t="s">
+        <v>55</v>
+      </c>
+      <c r="D58" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="E58" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="F58" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="G58" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="B59" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="C59" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="D59" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="E59" s="41" t="s">
+        <v>207</v>
+      </c>
+      <c r="F59" s="41" t="s">
+        <v>207</v>
+      </c>
+      <c r="G59" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="42" t="s">
+        <v>57</v>
+      </c>
+      <c r="B60" s="42" t="s">
+        <v>57</v>
+      </c>
+      <c r="C60" s="42" t="s">
+        <v>57</v>
+      </c>
+      <c r="D60" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="E60" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="F60" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="G60" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" s="41"/>
+      <c r="B61" s="41"/>
+      <c r="C61" s="41" t="s">
+        <v>208</v>
+      </c>
+      <c r="D61" s="42"/>
+      <c r="E61" s="42"/>
+      <c r="F61" s="42" t="s">
+        <v>203</v>
+      </c>
+      <c r="G61" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" s="42" t="s">
+        <v>58</v>
+      </c>
+      <c r="B62" s="42" t="s">
+        <v>58</v>
+      </c>
+      <c r="C62" s="42" t="s">
+        <v>58</v>
+      </c>
+      <c r="D62" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="E62" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="F62" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="G62" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" s="42" t="s">
+        <v>59</v>
+      </c>
+      <c r="B63" s="42" t="s">
+        <v>59</v>
+      </c>
+      <c r="C63" s="42" t="s">
+        <v>59</v>
+      </c>
+      <c r="D63" s="42" t="s">
+        <v>32</v>
+      </c>
+      <c r="E63" s="42" t="s">
+        <v>32</v>
+      </c>
+      <c r="F63" s="42" t="s">
+        <v>32</v>
+      </c>
+      <c r="G63" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" s="42" t="s">
+        <v>60</v>
+      </c>
+      <c r="B64" s="42" t="s">
+        <v>60</v>
+      </c>
+      <c r="C64" s="42" t="s">
+        <v>60</v>
+      </c>
+      <c r="D64" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="E64" s="41" t="s">
+        <v>209</v>
+      </c>
+      <c r="F64" s="41" t="s">
+        <v>209</v>
+      </c>
+      <c r="G64" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" s="41"/>
+      <c r="B65" s="41"/>
+      <c r="C65" s="41" t="s">
+        <v>210</v>
+      </c>
+      <c r="D65" s="41"/>
+      <c r="E65" s="41"/>
+      <c r="F65" s="42" t="s">
+        <v>203</v>
+      </c>
+      <c r="G65" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" s="42" t="s">
+        <v>61</v>
+      </c>
+      <c r="B66" s="42" t="s">
+        <v>61</v>
+      </c>
+      <c r="C66" s="42" t="s">
+        <v>61</v>
+      </c>
+      <c r="D66" s="42" t="s">
+        <v>26</v>
+      </c>
+      <c r="E66" s="42" t="s">
+        <v>203</v>
+      </c>
+      <c r="F66" s="42" t="s">
+        <v>203</v>
+      </c>
+      <c r="G66" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" s="42" t="s">
+        <v>62</v>
+      </c>
+      <c r="B67" s="42" t="s">
+        <v>62</v>
+      </c>
+      <c r="C67" s="42" t="s">
+        <v>62</v>
+      </c>
+      <c r="D67" s="42" t="s">
+        <v>26</v>
+      </c>
+      <c r="E67" s="42" t="s">
+        <v>203</v>
+      </c>
+      <c r="F67" s="42" t="s">
+        <v>203</v>
+      </c>
+      <c r="G67" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="42" t="s">
+        <v>63</v>
+      </c>
+      <c r="B68" s="42" t="s">
+        <v>63</v>
+      </c>
+      <c r="C68" s="42" t="s">
+        <v>63</v>
+      </c>
+      <c r="D68" s="41" t="s">
+        <v>117</v>
+      </c>
+      <c r="E68" s="41" t="s">
+        <v>211</v>
+      </c>
+      <c r="F68" s="41" t="s">
+        <v>211</v>
+      </c>
+      <c r="G68" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="41"/>
+      <c r="B69" s="41"/>
+      <c r="C69" s="41" t="s">
+        <v>212</v>
+      </c>
+      <c r="D69" s="41"/>
+      <c r="E69" s="41"/>
+      <c r="F69" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="G69" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="B70" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="C70" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="D70" s="41" t="s">
+        <v>117</v>
+      </c>
+      <c r="E70" s="41" t="s">
+        <v>213</v>
+      </c>
+      <c r="F70" s="41" t="s">
+        <v>213</v>
+      </c>
+      <c r="G70" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="B71" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="C71" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="D71" s="42" t="s">
+        <v>31</v>
+      </c>
+      <c r="E71" s="42" t="s">
+        <v>31</v>
+      </c>
+      <c r="F71" s="42" t="s">
+        <v>31</v>
+      </c>
+      <c r="G71" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="41"/>
+      <c r="B72" s="41"/>
+      <c r="C72" s="41" t="s">
+        <v>214</v>
+      </c>
+      <c r="D72" s="42"/>
+      <c r="E72" s="42"/>
+      <c r="F72" s="42" t="s">
+        <v>203</v>
+      </c>
+      <c r="G72" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="42" t="s">
+        <v>66</v>
+      </c>
+      <c r="B73" s="42" t="s">
+        <v>66</v>
+      </c>
+      <c r="C73" s="42" t="s">
+        <v>66</v>
+      </c>
+      <c r="D73" s="42" t="s">
+        <v>29</v>
+      </c>
+      <c r="E73" s="42" t="s">
+        <v>29</v>
+      </c>
+      <c r="F73" s="42" t="s">
+        <v>29</v>
+      </c>
+      <c r="G73" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="B74" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="C74" s="41"/>
+      <c r="D74" s="42" t="s">
+        <v>26</v>
+      </c>
+      <c r="E74" s="42" t="s">
+        <v>203</v>
+      </c>
+      <c r="F74" s="42"/>
+      <c r="G74" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" s="41" t="s">
+        <v>68</v>
+      </c>
+      <c r="B75" s="41" t="s">
+        <v>68</v>
+      </c>
+      <c r="C75" s="41"/>
+      <c r="D75" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="E75" s="42" t="s">
+        <v>215</v>
+      </c>
+      <c r="F75" s="42"/>
+      <c r="G75" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" s="41"/>
+      <c r="B76" s="41"/>
+      <c r="C76" s="41" t="s">
+        <v>216</v>
+      </c>
+      <c r="D76" s="42"/>
+      <c r="E76" s="42"/>
+      <c r="F76" s="42" t="s">
+        <v>217</v>
+      </c>
+      <c r="G76" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="B77" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="C77" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="D77" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="E77" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="F77" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="G77" s="43" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" s="44" t="s">
+        <v>86</v>
+      </c>
+      <c r="B78" s="44" t="s">
+        <v>86</v>
+      </c>
+      <c r="C78" s="44" t="s">
+        <v>86</v>
+      </c>
+      <c r="D78" s="44" t="s">
+        <v>86</v>
+      </c>
+      <c r="E78" s="44" t="s">
+        <v>86</v>
+      </c>
+      <c r="F78" s="44" t="s">
+        <v>86</v>
+      </c>
+      <c r="G78" s="44" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="B79" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="C79" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="D79" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="E79" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="F79" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="G79" s="44" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" s="44" t="s">
+        <v>88</v>
+      </c>
+      <c r="B80" s="44" t="s">
+        <v>88</v>
+      </c>
+      <c r="C80" s="44" t="s">
+        <v>88</v>
+      </c>
+      <c r="D80" s="44" t="s">
+        <v>88</v>
+      </c>
+      <c r="E80" s="44" t="s">
+        <v>88</v>
+      </c>
+      <c r="F80" s="44" t="s">
+        <v>88</v>
+      </c>
+      <c r="G80" s="44" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A81" s="44" t="s">
+        <v>89</v>
+      </c>
+      <c r="B81" s="44" t="s">
+        <v>89</v>
+      </c>
+      <c r="C81" s="44" t="s">
+        <v>89</v>
+      </c>
+      <c r="D81" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="E81" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="F81" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="G81" s="44" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A82" s="44" t="s">
+        <v>90</v>
+      </c>
+      <c r="B82" s="44" t="s">
+        <v>90</v>
+      </c>
+      <c r="C82" s="44" t="s">
+        <v>90</v>
+      </c>
+      <c r="D82" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="E82" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="F82" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="G82" s="44" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A83" s="44" t="s">
+        <v>91</v>
+      </c>
+      <c r="B83" s="44" t="s">
+        <v>91</v>
+      </c>
+      <c r="C83" s="44" t="s">
+        <v>91</v>
+      </c>
+      <c r="D83" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="E83" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="F83" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="G83" s="44" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A84" s="44" t="s">
+        <v>92</v>
+      </c>
+      <c r="B84" s="44" t="s">
+        <v>92</v>
+      </c>
+      <c r="C84" s="44" t="s">
+        <v>92</v>
+      </c>
+      <c r="D84" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="E84" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="F84" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="G84" s="44" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A85" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="B85" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="C85" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="D85" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="E85" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="F85" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="G85" s="44" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86" s="44" t="s">
+        <v>94</v>
+      </c>
+      <c r="B86" s="44" t="s">
+        <v>94</v>
+      </c>
+      <c r="C86" s="44" t="s">
+        <v>94</v>
+      </c>
+      <c r="D86" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="E86" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="F86" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="G86" s="44" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A87" s="44" t="s">
+        <v>95</v>
+      </c>
+      <c r="B87" s="44" t="s">
+        <v>95</v>
+      </c>
+      <c r="C87" s="44" t="s">
+        <v>95</v>
+      </c>
+      <c r="D87" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="E87" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="F87" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="G87" s="44" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A88" s="44" t="s">
+        <v>96</v>
+      </c>
+      <c r="B88" s="44" t="s">
+        <v>96</v>
+      </c>
+      <c r="C88" s="44" t="s">
+        <v>96</v>
+      </c>
+      <c r="D88" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="E88" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="F88" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="G88" s="44" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A89" s="44" t="s">
+        <v>97</v>
+      </c>
+      <c r="B89" s="44" t="s">
+        <v>97</v>
+      </c>
+      <c r="C89" s="44" t="s">
+        <v>97</v>
+      </c>
+      <c r="D89" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="E89" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="F89" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="G89" s="44" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A90" s="44" t="s">
+        <v>98</v>
+      </c>
+      <c r="B90" s="44" t="s">
+        <v>98</v>
+      </c>
+      <c r="C90" s="44" t="s">
+        <v>98</v>
+      </c>
+      <c r="D90" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="E90" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="F90" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="G90" s="44" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A91" s="44" t="s">
+        <v>99</v>
+      </c>
+      <c r="B91" s="44" t="s">
+        <v>99</v>
+      </c>
+      <c r="C91" s="44" t="s">
+        <v>99</v>
+      </c>
+      <c r="D91" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="E91" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="F91" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="G91" s="44" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A92" s="44" t="s">
+        <v>100</v>
+      </c>
+      <c r="B92" s="44" t="s">
+        <v>100</v>
+      </c>
+      <c r="C92" s="44" t="s">
+        <v>100</v>
+      </c>
+      <c r="D92" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="E92" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="F92" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="G92" s="44" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A93" s="44" t="s">
+        <v>101</v>
+      </c>
+      <c r="B93" s="44" t="s">
+        <v>101</v>
+      </c>
+      <c r="C93" s="44" t="s">
+        <v>101</v>
+      </c>
+      <c r="D93" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="E93" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="F93" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="G93" s="44" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A94" s="44" t="s">
+        <v>102</v>
+      </c>
+      <c r="B94" s="44" t="s">
+        <v>102</v>
+      </c>
+      <c r="C94" s="44" t="s">
+        <v>102</v>
+      </c>
+      <c r="D94" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="E94" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="F94" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="G94" s="44" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A95" s="44" t="s">
+        <v>103</v>
+      </c>
+      <c r="B95" s="44" t="s">
+        <v>103</v>
+      </c>
+      <c r="C95" s="44" t="s">
+        <v>103</v>
+      </c>
+      <c r="D95" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="E95" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="F95" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="G95" s="44" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A96" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="B96" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="C96" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="D96" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="E96" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="F96" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="G96" s="44" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A97" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="B97" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="C97" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="D97" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="E97" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="F97" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="G97" s="44" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="44" t="s">
+        <v>106</v>
+      </c>
+      <c r="B98" s="44" t="s">
+        <v>106</v>
+      </c>
+      <c r="C98" s="44" t="s">
+        <v>106</v>
+      </c>
+      <c r="D98" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="E98" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="F98" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="G98" s="44" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="B99" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="C99" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="D99" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="E99" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="F99" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="G99" s="44" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="44" t="s">
+        <v>218</v>
+      </c>
+      <c r="B100" s="44" t="s">
+        <v>218</v>
+      </c>
+      <c r="C100" s="44"/>
+      <c r="D100" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="E100" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="F100" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="G100" s="44" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="44" t="s">
+        <v>109</v>
+      </c>
+      <c r="B101" s="44" t="s">
+        <v>109</v>
+      </c>
+      <c r="C101" s="44" t="s">
+        <v>109</v>
+      </c>
+      <c r="D101" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="E101" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="F101" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="G101" s="44" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>77</v>
+      </c>
+      <c r="B102" t="s">
+        <v>77</v>
+      </c>
+      <c r="C102" t="s">
+        <v>77</v>
+      </c>
+      <c r="D102" t="s">
+        <v>78</v>
+      </c>
+      <c r="E102" t="s">
+        <v>219</v>
+      </c>
+      <c r="F102" t="s">
+        <v>219</v>
+      </c>
+      <c r="G102" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A103" s="45" t="s">
+        <v>69</v>
+      </c>
+      <c r="B103" s="45" t="s">
+        <v>69</v>
+      </c>
+      <c r="C103" s="45" t="s">
+        <v>69</v>
+      </c>
+      <c r="D103" s="45" t="s">
+        <v>23</v>
+      </c>
+      <c r="E103" s="45" t="s">
+        <v>23</v>
+      </c>
+      <c r="F103" s="45" t="s">
+        <v>23</v>
+      </c>
+      <c r="G103" s="45" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A104" s="45" t="s">
+        <v>70</v>
+      </c>
+      <c r="B104" s="45" t="s">
+        <v>70</v>
+      </c>
+      <c r="C104" s="45" t="s">
+        <v>70</v>
+      </c>
+      <c r="D104" s="45" t="s">
+        <v>25</v>
+      </c>
+      <c r="E104" s="45" t="s">
+        <v>25</v>
+      </c>
+      <c r="F104" s="45" t="s">
+        <v>25</v>
+      </c>
+      <c r="G104" s="45" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A105" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="B105" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="C105" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="D105" s="41" t="s">
+        <v>80</v>
+      </c>
+      <c r="E105" s="41" t="s">
+        <v>221</v>
+      </c>
+      <c r="F105" s="41" t="s">
+        <v>221</v>
+      </c>
+      <c r="G105" s="45" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A106" s="41" t="s">
+        <v>72</v>
+      </c>
+      <c r="B106" s="41" t="s">
+        <v>222</v>
+      </c>
+      <c r="C106" s="41" t="s">
+        <v>222</v>
+      </c>
+      <c r="D106" s="45" t="s">
+        <v>24</v>
+      </c>
+      <c r="E106" s="45" t="s">
+        <v>24</v>
+      </c>
+      <c r="F106" s="45" t="s">
+        <v>24</v>
+      </c>
+      <c r="G106" s="45" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A107" s="41"/>
+      <c r="B107" s="41"/>
+      <c r="C107" s="41" t="s">
+        <v>223</v>
+      </c>
+      <c r="D107" s="45"/>
+      <c r="E107" s="45"/>
+      <c r="F107" s="45" t="s">
+        <v>224</v>
+      </c>
+      <c r="G107" s="45" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A108" s="41"/>
+      <c r="B108" s="41"/>
+      <c r="C108" s="41" t="s">
+        <v>225</v>
+      </c>
+      <c r="D108" s="45"/>
+      <c r="E108" s="45"/>
+      <c r="F108" s="45" t="s">
+        <v>24</v>
+      </c>
+      <c r="G108" s="45" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A109" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="B109" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="C109" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="D109" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="E109" s="45" t="s">
+        <v>226</v>
+      </c>
+      <c r="F109" s="45" t="s">
+        <v>224</v>
+      </c>
+      <c r="G109" s="45" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A110" s="45" t="s">
+        <v>74</v>
+      </c>
+      <c r="B110" s="45" t="s">
+        <v>74</v>
+      </c>
+      <c r="C110" s="45" t="s">
+        <v>74</v>
+      </c>
+      <c r="D110" s="41" t="s">
+        <v>80</v>
+      </c>
+      <c r="E110" s="41" t="s">
+        <v>227</v>
+      </c>
+      <c r="F110" s="41" t="s">
+        <v>227</v>
+      </c>
+      <c r="G110" s="45" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A111" s="45" t="s">
+        <v>75</v>
+      </c>
+      <c r="B111" s="45" t="s">
+        <v>75</v>
+      </c>
+      <c r="C111" s="45"/>
+      <c r="D111" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="E111" s="45" t="s">
+        <v>226</v>
+      </c>
+      <c r="F111" s="45" t="s">
+        <v>224</v>
+      </c>
+      <c r="G111" s="45" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A112" s="45"/>
+      <c r="B112" s="45"/>
+      <c r="C112" s="45" t="s">
+        <v>228</v>
+      </c>
+      <c r="D112" s="45"/>
+      <c r="E112" s="45"/>
+      <c r="F112" s="45" t="s">
+        <v>224</v>
+      </c>
+      <c r="G112" s="45" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A113" s="46" t="s">
+        <v>76</v>
+      </c>
+      <c r="B113" s="46" t="s">
+        <v>76</v>
+      </c>
+      <c r="C113" s="46" t="s">
+        <v>76</v>
+      </c>
+      <c r="D113" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="E113" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="F113" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="G113" s="46" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>229</v>
+      </c>
+      <c r="B114" t="s">
+        <v>229</v>
+      </c>
+      <c r="C114" t="s">
+        <v>229</v>
+      </c>
+      <c r="D114" t="s">
+        <v>229</v>
+      </c>
+      <c r="E114" t="s">
+        <v>229</v>
+      </c>
+      <c r="F114" t="s">
+        <v>229</v>
+      </c>
+      <c r="G114" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A115" s="47" t="s">
+        <v>37</v>
+      </c>
+      <c r="B115" s="47" t="s">
+        <v>37</v>
+      </c>
+      <c r="C115" s="47" t="s">
+        <v>37</v>
+      </c>
+      <c r="D115" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="E115" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="F115" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="G115" s="47" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;13&amp;K000000 Confidential - Low</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0B059E5-D350-4A25-BADF-68475874AD58}">
   <dimension ref="B1:E69"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="38.85546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="60.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="2.28515625" customWidth="1"/>
+    <col min="2" max="2" width="38.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="60.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:5" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="38" t="s">
         <v>127</v>
       </c>
-      <c r="C2" s="37" t="s">
+      <c r="C2" s="36" t="s">
         <v>134</v>
       </c>
-      <c r="D2" s="37"/>
-      <c r="E2" s="38"/>
-    </row>
-    <row r="3" spans="2:5" s="2" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="40"/>
-      <c r="C3" s="9" t="s">
+      <c r="D2" s="36"/>
+      <c r="E2" s="37"/>
+    </row>
+    <row r="3" spans="2:5" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="39"/>
+      <c r="C3" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="10" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="4" spans="2:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="36" t="s">
+      <c r="B4" s="35" t="s">
         <v>128</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="D4" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="E4" s="14" t="s">
+      <c r="D4" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="E4" s="13" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="5" spans="2:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="36"/>
-      <c r="C5" s="15" t="s">
+      <c r="B5" s="35"/>
+      <c r="C5" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E5" s="17" t="s">
+      <c r="D5" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E5" s="16" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="6" spans="2:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="36"/>
-      <c r="C6" s="15" t="s">
+      <c r="B6" s="35"/>
+      <c r="C6" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="D6" s="16"/>
-      <c r="E6" s="17" t="s">
+      <c r="D6" s="15"/>
+      <c r="E6" s="16" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="7" spans="2:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="36"/>
-      <c r="C7" s="15" t="s">
+      <c r="B7" s="35"/>
+      <c r="C7" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="16" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="8" spans="2:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="36"/>
-      <c r="C8" s="15" t="s">
+      <c r="B8" s="35"/>
+      <c r="C8" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E8" s="17" t="s">
+      <c r="D8" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E8" s="16" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="9" spans="2:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="36"/>
-      <c r="C9" s="15" t="s">
+      <c r="B9" s="35"/>
+      <c r="C9" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="D9" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E9" s="17" t="s">
+      <c r="D9" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E9" s="16" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="10" spans="2:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="36"/>
-      <c r="C10" s="15" t="s">
+      <c r="B10" s="35"/>
+      <c r="C10" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="D10" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E10" s="17" t="s">
+      <c r="D10" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E10" s="16" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="11" spans="2:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="36"/>
-      <c r="C11" s="15" t="s">
+      <c r="B11" s="35"/>
+      <c r="C11" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="E11" s="17" t="s">
+      <c r="E11" s="16" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="12" spans="2:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="36"/>
-      <c r="C12" s="18" t="s">
+      <c r="B12" s="35"/>
+      <c r="C12" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="E12" s="20" t="s">
+      <c r="E12" s="19" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="13" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="36" t="s">
+      <c r="B13" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="13" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="14" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="36"/>
-      <c r="C14" s="15" t="s">
+      <c r="B14" s="35"/>
+      <c r="C14" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="E14" s="17" t="s">
+      <c r="E14" s="16" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="15" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="36"/>
-      <c r="C15" s="15" t="s">
+      <c r="B15" s="35"/>
+      <c r="C15" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D15" s="16" t="s">
+      <c r="D15" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="E15" s="17" t="s">
+      <c r="E15" s="16" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="16" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="36"/>
-      <c r="C16" s="15" t="s">
+      <c r="B16" s="35"/>
+      <c r="C16" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E16" s="17" t="s">
+      <c r="E16" s="16" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="17" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="36"/>
-      <c r="C17" s="15" t="s">
+      <c r="B17" s="35"/>
+      <c r="C17" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="D17" s="16" t="s">
+      <c r="D17" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="E17" s="17" t="s">
+      <c r="E17" s="16" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="18" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="36"/>
-      <c r="C18" s="15" t="s">
+      <c r="B18" s="35"/>
+      <c r="C18" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="D18" s="16" t="s">
+      <c r="D18" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="E18" s="17" t="s">
+      <c r="E18" s="16" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="19" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="36"/>
-      <c r="C19" s="15" t="s">
+      <c r="B19" s="35"/>
+      <c r="C19" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="D19" s="16" t="s">
+      <c r="D19" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="E19" s="17" t="s">
+      <c r="E19" s="16" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="20" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="36"/>
-      <c r="C20" s="15" t="s">
+      <c r="B20" s="35"/>
+      <c r="C20" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="D20" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="E20" s="17" t="s">
+      <c r="E20" s="16" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="21" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="36"/>
-      <c r="C21" s="21" t="s">
+      <c r="B21" s="35"/>
+      <c r="C21" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="D21" s="22" t="s">
+      <c r="D21" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="E21" s="23" t="s">
+      <c r="E21" s="22" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="22" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="36"/>
-      <c r="C22" s="21" t="s">
+      <c r="B22" s="35"/>
+      <c r="C22" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="D22" s="22" t="s">
+      <c r="D22" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="E22" s="23" t="s">
+      <c r="E22" s="22" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="23" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="36"/>
-      <c r="C23" s="24" t="s">
+      <c r="B23" s="35"/>
+      <c r="C23" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="D23" s="25" t="s">
+      <c r="D23" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="E23" s="26" t="s">
+      <c r="E23" s="25" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="24" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="36"/>
-      <c r="C24" s="24" t="s">
+      <c r="B24" s="35"/>
+      <c r="C24" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="D24" s="25" t="s">
+      <c r="D24" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="E24" s="26" t="s">
+      <c r="E24" s="25" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="25" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="36"/>
-      <c r="C25" s="24" t="s">
+      <c r="B25" s="35"/>
+      <c r="C25" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="D25" s="25" t="s">
+      <c r="D25" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="E25" s="26" t="s">
+      <c r="E25" s="25" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="26" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="36"/>
-      <c r="C26" s="24" t="s">
+      <c r="B26" s="35"/>
+      <c r="C26" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="D26" s="25" t="s">
+      <c r="D26" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="E26" s="26" t="s">
+      <c r="E26" s="25" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="27" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="36"/>
-      <c r="C27" s="27" t="s">
+      <c r="B27" s="35"/>
+      <c r="C27" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="D27" s="28" t="s">
+      <c r="D27" s="27" t="s">
         <v>119</v>
       </c>
-      <c r="E27" s="29" t="s">
+      <c r="E27" s="28" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="28" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="36"/>
-      <c r="C28" s="27" t="s">
+      <c r="B28" s="35"/>
+      <c r="C28" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="D28" s="28" t="s">
+      <c r="D28" s="27" t="s">
         <v>120</v>
       </c>
-      <c r="E28" s="29" t="s">
+      <c r="E28" s="28" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="29" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="36"/>
-      <c r="C29" s="27" t="s">
+      <c r="B29" s="35"/>
+      <c r="C29" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="D29" s="28" t="s">
-        <v>114</v>
-      </c>
-      <c r="E29" s="29" t="s">
+      <c r="D29" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="E29" s="28" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="30" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="36"/>
-      <c r="C30" s="27" t="s">
+      <c r="B30" s="35"/>
+      <c r="C30" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="D30" s="28" t="s">
-        <v>114</v>
-      </c>
-      <c r="E30" s="29" t="s">
+      <c r="D30" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="E30" s="28" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="31" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="36"/>
-      <c r="C31" s="27" t="s">
+      <c r="B31" s="35"/>
+      <c r="C31" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="D31" s="28" t="s">
-        <v>114</v>
-      </c>
-      <c r="E31" s="29" t="s">
+      <c r="D31" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="E31" s="28" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="32" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="36"/>
-      <c r="C32" s="27" t="s">
+      <c r="B32" s="35"/>
+      <c r="C32" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="D32" s="28" t="s">
-        <v>114</v>
-      </c>
-      <c r="E32" s="29" t="s">
+      <c r="D32" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="E32" s="28" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="33" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="36"/>
-      <c r="C33" s="27" t="s">
+      <c r="B33" s="35"/>
+      <c r="C33" s="26" t="s">
         <v>67</v>
       </c>
-      <c r="D33" s="28" t="s">
+      <c r="D33" s="27" t="s">
         <v>115</v>
       </c>
-      <c r="E33" s="29" t="s">
+      <c r="E33" s="28" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="34" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="36"/>
-      <c r="C34" s="18" t="s">
+      <c r="B34" s="35"/>
+      <c r="C34" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D34" s="19" t="s">
+      <c r="D34" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="E34" s="20" t="s">
+      <c r="E34" s="19" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="35" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="36" t="s">
+      <c r="B35" s="35" t="s">
         <v>129</v>
       </c>
-      <c r="C35" s="12" t="s">
+      <c r="C35" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="D35" s="13" t="s">
+      <c r="D35" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="E35" s="14" t="s">
+      <c r="E35" s="13" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="36" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="36"/>
-      <c r="C36" s="15" t="s">
+      <c r="B36" s="35"/>
+      <c r="C36" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="D36" s="16" t="s">
+      <c r="D36" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="E36" s="17" t="s">
+      <c r="E36" s="16" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="37" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="36"/>
-      <c r="C37" s="15" t="s">
+      <c r="B37" s="35"/>
+      <c r="C37" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="D37" s="16" t="s">
+      <c r="D37" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="E37" s="17" t="s">
+      <c r="E37" s="16" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="38" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="36"/>
-      <c r="C38" s="30" t="s">
+      <c r="B38" s="35"/>
+      <c r="C38" s="29" t="s">
         <v>71</v>
       </c>
-      <c r="D38" s="31" t="s">
+      <c r="D38" s="30" t="s">
         <v>136</v>
       </c>
-      <c r="E38" s="32" t="s">
+      <c r="E38" s="31" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="39" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="36"/>
-      <c r="C39" s="30" t="s">
+      <c r="B39" s="35"/>
+      <c r="C39" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="D39" s="31" t="s">
+      <c r="D39" s="30" t="s">
         <v>136</v>
       </c>
-      <c r="E39" s="32" t="s">
+      <c r="E39" s="31" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="40" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="36"/>
-      <c r="C40" s="30" t="s">
+      <c r="B40" s="35"/>
+      <c r="C40" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="D40" s="31" t="s">
+      <c r="D40" s="30" t="s">
         <v>136</v>
       </c>
-      <c r="E40" s="32" t="s">
+      <c r="E40" s="31" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="41" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="36"/>
-      <c r="C41" s="30" t="s">
+      <c r="B41" s="35"/>
+      <c r="C41" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="D41" s="31" t="s">
+      <c r="D41" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="E41" s="32" t="s">
+      <c r="E41" s="31" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="42" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="36"/>
-      <c r="C42" s="33" t="s">
-        <v>114</v>
-      </c>
-      <c r="D42" s="34" t="s">
+      <c r="B42" s="35"/>
+      <c r="C42" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="D42" s="33" t="s">
         <v>83</v>
       </c>
-      <c r="E42" s="35" t="s">
+      <c r="E42" s="34" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="43" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="8" t="s">
+      <c r="B43" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="C43" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D43" s="3" t="s">
+      <c r="D43" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E43" s="5" t="s">
+      <c r="E43" s="4" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="44" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="8" t="s">
+      <c r="B44" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="C44" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
+      <c r="D44" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E44" s="5" t="s">
+      <c r="E44" s="4" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="45" spans="2:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B45" s="8" t="s">
+      <c r="B45" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="C45" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="D45" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E45" s="5" t="s">
+      <c r="E45" s="4" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="46" spans="2:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="8" t="s">
+      <c r="B46" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="C46" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D46" s="3" t="s">
+      <c r="D46" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E46" s="5" t="s">
+      <c r="E46" s="4" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="47" spans="2:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B47" s="36" t="s">
+      <c r="B47" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="C47" s="12" t="s">
+      <c r="C47" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="D47" s="13" t="s">
+      <c r="D47" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="E47" s="14" t="s">
+      <c r="E47" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="48" spans="2:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="36"/>
-      <c r="C48" s="15" t="s">
+      <c r="B48" s="35"/>
+      <c r="C48" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="D48" s="16" t="s">
+      <c r="D48" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="E48" s="17" t="s">
+      <c r="E48" s="16" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="49" spans="2:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="36"/>
-      <c r="C49" s="15" t="s">
+      <c r="B49" s="35"/>
+      <c r="C49" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="D49" s="16" t="s">
+      <c r="D49" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="E49" s="17" t="s">
+      <c r="E49" s="16" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="50" spans="2:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="36"/>
-      <c r="C50" s="15" t="s">
+      <c r="B50" s="35"/>
+      <c r="C50" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="D50" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E50" s="17" t="s">
+      <c r="D50" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E50" s="16" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="51" spans="2:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B51" s="36"/>
-      <c r="C51" s="15" t="s">
+      <c r="B51" s="35"/>
+      <c r="C51" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="D51" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E51" s="17" t="s">
+      <c r="D51" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E51" s="16" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="52" spans="2:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="36"/>
-      <c r="C52" s="15" t="s">
+      <c r="B52" s="35"/>
+      <c r="C52" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="D52" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E52" s="17" t="s">
+      <c r="D52" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E52" s="16" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="53" spans="2:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B53" s="36"/>
-      <c r="C53" s="15" t="s">
+      <c r="B53" s="35"/>
+      <c r="C53" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="D53" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E53" s="17" t="s">
+      <c r="D53" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E53" s="16" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="54" spans="2:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="36"/>
-      <c r="C54" s="15" t="s">
+      <c r="B54" s="35"/>
+      <c r="C54" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="D54" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E54" s="17" t="s">
+      <c r="D54" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E54" s="16" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="55" spans="2:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="36"/>
-      <c r="C55" s="15" t="s">
+      <c r="B55" s="35"/>
+      <c r="C55" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="D55" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E55" s="17" t="s">
+      <c r="D55" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E55" s="16" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="56" spans="2:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="36"/>
-      <c r="C56" s="15" t="s">
+      <c r="B56" s="35"/>
+      <c r="C56" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="D56" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E56" s="17" t="s">
+      <c r="D56" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E56" s="16" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="57" spans="2:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="36"/>
-      <c r="C57" s="15" t="s">
+      <c r="B57" s="35"/>
+      <c r="C57" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="D57" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E57" s="17" t="s">
+      <c r="D57" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E57" s="16" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="58" spans="2:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="36"/>
-      <c r="C58" s="15" t="s">
+      <c r="B58" s="35"/>
+      <c r="C58" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="D58" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E58" s="17" t="s">
+      <c r="D58" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E58" s="16" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="59" spans="2:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="36"/>
-      <c r="C59" s="15" t="s">
+      <c r="B59" s="35"/>
+      <c r="C59" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="D59" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E59" s="17" t="s">
+      <c r="D59" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E59" s="16" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="60" spans="2:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="36"/>
-      <c r="C60" s="15" t="s">
+      <c r="B60" s="35"/>
+      <c r="C60" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="D60" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E60" s="17" t="s">
+      <c r="D60" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E60" s="16" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="61" spans="2:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="36"/>
-      <c r="C61" s="15" t="s">
+      <c r="B61" s="35"/>
+      <c r="C61" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="D61" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E61" s="17" t="s">
+      <c r="D61" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E61" s="16" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="62" spans="2:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="36"/>
-      <c r="C62" s="15" t="s">
+      <c r="B62" s="35"/>
+      <c r="C62" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="D62" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E62" s="17" t="s">
+      <c r="D62" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E62" s="16" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="63" spans="2:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B63" s="36"/>
-      <c r="C63" s="15" t="s">
+      <c r="B63" s="35"/>
+      <c r="C63" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="D63" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E63" s="17" t="s">
+      <c r="D63" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E63" s="16" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="64" spans="2:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="36"/>
-      <c r="C64" s="15" t="s">
+      <c r="B64" s="35"/>
+      <c r="C64" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="D64" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E64" s="17" t="s">
+      <c r="D64" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E64" s="16" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="65" spans="2:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="36"/>
-      <c r="C65" s="15" t="s">
+      <c r="B65" s="35"/>
+      <c r="C65" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="D65" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E65" s="17" t="s">
+      <c r="D65" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E65" s="16" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="66" spans="2:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B66" s="36"/>
-      <c r="C66" s="15" t="s">
+      <c r="B66" s="35"/>
+      <c r="C66" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="D66" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E66" s="17" t="s">
+      <c r="D66" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E66" s="16" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="67" spans="2:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B67" s="36"/>
-      <c r="C67" s="15" t="s">
+      <c r="B67" s="35"/>
+      <c r="C67" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="D67" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E67" s="17" t="s">
+      <c r="D67" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E67" s="16" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="68" spans="2:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="36"/>
-      <c r="C68" s="15" t="s">
+      <c r="B68" s="35"/>
+      <c r="C68" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="D68" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="E68" s="17" t="s">
+      <c r="D68" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E68" s="16" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="69" spans="2:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B69" s="36"/>
-      <c r="C69" s="18" t="s">
+      <c r="B69" s="35"/>
+      <c r="C69" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="D69" s="19" t="s">
+      <c r="D69" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="E69" s="20" t="s">
+      <c r="E69" s="19" t="s">
         <v>108</v>
       </c>
     </row>
@@ -2757,5 +5575,8 @@
     <mergeCell ref="B35:B42"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;13&amp;K000000 Confidential - Low</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>